--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467364</v>
+        <v>121467415</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455565</v>
+        <v>455772</v>
       </c>
       <c r="R2" t="n">
-        <v>7044803</v>
+        <v>7044856</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467414</v>
+        <v>121467364</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455774</v>
+        <v>455565</v>
       </c>
       <c r="R3" t="n">
-        <v>7044858</v>
+        <v>7044803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467365</v>
+        <v>121467424</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455435</v>
+        <v>455517</v>
       </c>
       <c r="R4" t="n">
-        <v>7044990</v>
+        <v>7044891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467415</v>
+        <v>121467414</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455772</v>
+        <v>455774</v>
       </c>
       <c r="R5" t="n">
-        <v>7044856</v>
+        <v>7044858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467424</v>
+        <v>121467416</v>
       </c>
       <c r="B6" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455517</v>
+        <v>455613</v>
       </c>
       <c r="R6" t="n">
-        <v>7044891</v>
+        <v>7044824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467413</v>
+        <v>121467365</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455781</v>
+        <v>455435</v>
       </c>
       <c r="R7" t="n">
-        <v>7044824</v>
+        <v>7044990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467416</v>
+        <v>121467413</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455613</v>
+        <v>455781</v>
       </c>
       <c r="R8" t="n">
         <v>7044824</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467415</v>
+        <v>121467416</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455772</v>
+        <v>455613</v>
       </c>
       <c r="R2" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467364</v>
+        <v>121467413</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455565</v>
+        <v>455781</v>
       </c>
       <c r="R3" t="n">
-        <v>7044803</v>
+        <v>7044824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467424</v>
+        <v>121467415</v>
       </c>
       <c r="B4" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455517</v>
+        <v>455772</v>
       </c>
       <c r="R4" t="n">
-        <v>7044891</v>
+        <v>7044856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467416</v>
+        <v>121467424</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455613</v>
+        <v>455517</v>
       </c>
       <c r="R6" t="n">
-        <v>7044824</v>
+        <v>7044891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467365</v>
+        <v>121467364</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455435</v>
+        <v>455565</v>
       </c>
       <c r="R7" t="n">
-        <v>7044990</v>
+        <v>7044803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467413</v>
+        <v>121467365</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455781</v>
+        <v>455435</v>
       </c>
       <c r="R8" t="n">
-        <v>7044824</v>
+        <v>7044990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467416</v>
+        <v>121467365</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455613</v>
+        <v>455435</v>
       </c>
       <c r="R2" t="n">
-        <v>7044824</v>
+        <v>7044990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467413</v>
+        <v>121467415</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455781</v>
+        <v>455772</v>
       </c>
       <c r="R3" t="n">
-        <v>7044824</v>
+        <v>7044856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467415</v>
+        <v>121467416</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455772</v>
+        <v>455613</v>
       </c>
       <c r="R4" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>121467414</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467424</v>
+        <v>121467413</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455517</v>
+        <v>455781</v>
       </c>
       <c r="R6" t="n">
-        <v>7044891</v>
+        <v>7044824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467364</v>
+        <v>121467424</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455565</v>
+        <v>455517</v>
       </c>
       <c r="R7" t="n">
-        <v>7044803</v>
+        <v>7044891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467365</v>
+        <v>121467364</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455435</v>
+        <v>455565</v>
       </c>
       <c r="R8" t="n">
-        <v>7044990</v>
+        <v>7044803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467365</v>
+        <v>121467424</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455435</v>
+        <v>455517</v>
       </c>
       <c r="R2" t="n">
-        <v>7044990</v>
+        <v>7044891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467415</v>
+        <v>121467416</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455772</v>
+        <v>455613</v>
       </c>
       <c r="R3" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467416</v>
+        <v>121467365</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455613</v>
+        <v>455435</v>
       </c>
       <c r="R4" t="n">
-        <v>7044824</v>
+        <v>7044990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467414</v>
+        <v>121467413</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455774</v>
+        <v>455781</v>
       </c>
       <c r="R5" t="n">
-        <v>7044858</v>
+        <v>7044824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467413</v>
+        <v>121467415</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455781</v>
+        <v>455772</v>
       </c>
       <c r="R6" t="n">
-        <v>7044824</v>
+        <v>7044856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467424</v>
+        <v>121467414</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455517</v>
+        <v>455774</v>
       </c>
       <c r="R7" t="n">
-        <v>7044891</v>
+        <v>7044858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467424</v>
+        <v>121467364</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455517</v>
+        <v>455565</v>
       </c>
       <c r="R2" t="n">
-        <v>7044891</v>
+        <v>7044803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467416</v>
+        <v>121467414</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455613</v>
+        <v>455774</v>
       </c>
       <c r="R3" t="n">
-        <v>7044824</v>
+        <v>7044858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467365</v>
+        <v>121467424</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455435</v>
+        <v>455517</v>
       </c>
       <c r="R4" t="n">
-        <v>7044990</v>
+        <v>7044891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467413</v>
+        <v>121467415</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455781</v>
+        <v>455772</v>
       </c>
       <c r="R5" t="n">
-        <v>7044824</v>
+        <v>7044856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467415</v>
+        <v>121467413</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455772</v>
+        <v>455781</v>
       </c>
       <c r="R6" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467414</v>
+        <v>121467416</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455774</v>
+        <v>455613</v>
       </c>
       <c r="R7" t="n">
-        <v>7044858</v>
+        <v>7044824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467364</v>
+        <v>121467365</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455565</v>
+        <v>455435</v>
       </c>
       <c r="R8" t="n">
-        <v>7044803</v>
+        <v>7044990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467364</v>
+        <v>121467416</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455565</v>
+        <v>455613</v>
       </c>
       <c r="R2" t="n">
-        <v>7044803</v>
+        <v>7044824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467414</v>
+        <v>121467424</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455774</v>
+        <v>455517</v>
       </c>
       <c r="R3" t="n">
-        <v>7044858</v>
+        <v>7044891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467424</v>
+        <v>121467364</v>
       </c>
       <c r="B4" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455517</v>
+        <v>455565</v>
       </c>
       <c r="R4" t="n">
-        <v>7044891</v>
+        <v>7044803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467415</v>
+        <v>121467413</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455772</v>
+        <v>455781</v>
       </c>
       <c r="R5" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467413</v>
+        <v>121467414</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455781</v>
+        <v>455774</v>
       </c>
       <c r="R6" t="n">
-        <v>7044824</v>
+        <v>7044858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467416</v>
+        <v>121467365</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455613</v>
+        <v>455435</v>
       </c>
       <c r="R7" t="n">
-        <v>7044824</v>
+        <v>7044990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467365</v>
+        <v>121467415</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455435</v>
+        <v>455772</v>
       </c>
       <c r="R8" t="n">
-        <v>7044990</v>
+        <v>7044856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467416</v>
+        <v>121467413</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455613</v>
+        <v>455781</v>
       </c>
       <c r="R2" t="n">
         <v>7044824</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467424</v>
+        <v>121467364</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455517</v>
+        <v>455565</v>
       </c>
       <c r="R3" t="n">
-        <v>7044891</v>
+        <v>7044803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467364</v>
+        <v>121467414</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455565</v>
+        <v>455774</v>
       </c>
       <c r="R4" t="n">
-        <v>7044803</v>
+        <v>7044858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467413</v>
+        <v>121467416</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1031,7 +1036,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455781</v>
+        <v>455613</v>
       </c>
       <c r="R5" t="n">
         <v>7044824</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467414</v>
+        <v>121467424</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455774</v>
+        <v>455517</v>
       </c>
       <c r="R6" t="n">
-        <v>7044858</v>
+        <v>7044891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467413</v>
+        <v>121467416</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455781</v>
+        <v>455613</v>
       </c>
       <c r="R2" t="n">
         <v>7044824</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467364</v>
+        <v>121467413</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455565</v>
+        <v>455781</v>
       </c>
       <c r="R3" t="n">
-        <v>7044803</v>
+        <v>7044824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467414</v>
+        <v>121467365</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455774</v>
+        <v>455435</v>
       </c>
       <c r="R4" t="n">
-        <v>7044858</v>
+        <v>7044990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467416</v>
+        <v>121467414</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455613</v>
+        <v>455774</v>
       </c>
       <c r="R5" t="n">
-        <v>7044824</v>
+        <v>7044858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467424</v>
+        <v>121467415</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455517</v>
+        <v>455772</v>
       </c>
       <c r="R6" t="n">
-        <v>7044891</v>
+        <v>7044856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467365</v>
+        <v>121467364</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455435</v>
+        <v>455565</v>
       </c>
       <c r="R7" t="n">
-        <v>7044990</v>
+        <v>7044803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467415</v>
+        <v>121467424</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455772</v>
+        <v>455517</v>
       </c>
       <c r="R8" t="n">
-        <v>7044856</v>
+        <v>7044891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467416</v>
+        <v>121467414</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455613</v>
+        <v>455774</v>
       </c>
       <c r="R2" t="n">
-        <v>7044824</v>
+        <v>7044858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467413</v>
+        <v>121467424</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455781</v>
+        <v>455517</v>
       </c>
       <c r="R3" t="n">
-        <v>7044824</v>
+        <v>7044891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467365</v>
+        <v>121467413</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455435</v>
+        <v>455781</v>
       </c>
       <c r="R4" t="n">
-        <v>7044990</v>
+        <v>7044824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467414</v>
+        <v>121467365</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455774</v>
+        <v>455435</v>
       </c>
       <c r="R5" t="n">
-        <v>7044858</v>
+        <v>7044990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467364</v>
+        <v>121467416</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455565</v>
+        <v>455613</v>
       </c>
       <c r="R7" t="n">
-        <v>7044803</v>
+        <v>7044824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467424</v>
+        <v>121467364</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455517</v>
+        <v>455565</v>
       </c>
       <c r="R8" t="n">
-        <v>7044891</v>
+        <v>7044803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467414</v>
+        <v>121467416</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455774</v>
+        <v>455613</v>
       </c>
       <c r="R2" t="n">
-        <v>7044858</v>
+        <v>7044824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467424</v>
+        <v>121467364</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455517</v>
+        <v>455565</v>
       </c>
       <c r="R3" t="n">
-        <v>7044891</v>
+        <v>7044803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467413</v>
+        <v>121467415</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455781</v>
+        <v>455772</v>
       </c>
       <c r="R4" t="n">
-        <v>7044824</v>
+        <v>7044856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467365</v>
+        <v>121467414</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455435</v>
+        <v>455774</v>
       </c>
       <c r="R5" t="n">
-        <v>7044990</v>
+        <v>7044858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467415</v>
+        <v>121467413</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455772</v>
+        <v>455781</v>
       </c>
       <c r="R6" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467416</v>
+        <v>121467424</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455613</v>
+        <v>455517</v>
       </c>
       <c r="R7" t="n">
-        <v>7044824</v>
+        <v>7044891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467364</v>
+        <v>121467365</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455565</v>
+        <v>455435</v>
       </c>
       <c r="R8" t="n">
-        <v>7044803</v>
+        <v>7044990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467414</v>
+        <v>121467416</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455774</v>
+        <v>455613</v>
       </c>
       <c r="R2" t="n">
-        <v>7044858</v>
+        <v>7044824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467364</v>
+        <v>121467424</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455565</v>
+        <v>455517</v>
       </c>
       <c r="R3" t="n">
-        <v>7044803</v>
+        <v>7044891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467424</v>
+        <v>121467365</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455517</v>
+        <v>455435</v>
       </c>
       <c r="R4" t="n">
-        <v>7044891</v>
+        <v>7044990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467413</v>
+        <v>121467415</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455781</v>
+        <v>455772</v>
       </c>
       <c r="R5" t="n">
-        <v>7044824</v>
+        <v>7044856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467415</v>
+        <v>121467413</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455772</v>
+        <v>455781</v>
       </c>
       <c r="R6" t="n">
-        <v>7044856</v>
+        <v>7044824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467416</v>
+        <v>121467364</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455613</v>
+        <v>455565</v>
       </c>
       <c r="R7" t="n">
-        <v>7044824</v>
+        <v>7044803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467365</v>
+        <v>121467414</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455435</v>
+        <v>455774</v>
       </c>
       <c r="R8" t="n">
-        <v>7044990</v>
+        <v>7044858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467416</v>
+        <v>121467413</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455613</v>
+        <v>455781</v>
       </c>
       <c r="R2" t="n">
         <v>7044824</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467424</v>
+        <v>121467364</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455517</v>
+        <v>455565</v>
       </c>
       <c r="R3" t="n">
-        <v>7044891</v>
+        <v>7044803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467365</v>
+        <v>121467416</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455435</v>
+        <v>455613</v>
       </c>
       <c r="R4" t="n">
-        <v>7044990</v>
+        <v>7044824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467415</v>
+        <v>121467424</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455772</v>
+        <v>455517</v>
       </c>
       <c r="R5" t="n">
-        <v>7044856</v>
+        <v>7044891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467413</v>
+        <v>121467414</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455781</v>
+        <v>455774</v>
       </c>
       <c r="R6" t="n">
-        <v>7044824</v>
+        <v>7044858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467364</v>
+        <v>121467365</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455565</v>
+        <v>455435</v>
       </c>
       <c r="R7" t="n">
-        <v>7044803</v>
+        <v>7044990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467414</v>
+        <v>121467415</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455774</v>
+        <v>455772</v>
       </c>
       <c r="R8" t="n">
-        <v>7044858</v>
+        <v>7044856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467413</v>
+        <v>121467364</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455781</v>
+        <v>455565</v>
       </c>
       <c r="R2" t="n">
-        <v>7044824</v>
+        <v>7044803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467364</v>
+        <v>121467365</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455565</v>
+        <v>455435</v>
       </c>
       <c r="R3" t="n">
-        <v>7044803</v>
+        <v>7044990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467416</v>
+        <v>121467413</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,7 +914,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455613</v>
+        <v>455781</v>
       </c>
       <c r="R4" t="n">
         <v>7044824</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467424</v>
+        <v>121467414</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455517</v>
+        <v>455774</v>
       </c>
       <c r="R5" t="n">
-        <v>7044891</v>
+        <v>7044858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467414</v>
+        <v>121467415</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455774</v>
+        <v>455772</v>
       </c>
       <c r="R6" t="n">
-        <v>7044858</v>
+        <v>7044856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467365</v>
+        <v>121467416</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455435</v>
+        <v>455613</v>
       </c>
       <c r="R7" t="n">
-        <v>7044990</v>
+        <v>7044824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,113 +1284,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>121467415</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>455772</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7044856</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49386-2024 artfynd.xlsx
+++ b/artfynd/A 49386-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467414</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467416</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>